--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -645,7 +645,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -739,7 +739,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -824,7 +824,7 @@
     <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
-    <t>処方箋に対するID</t>
+    <t>全国で⼀意となる処方箋ID</t>
   </si>
   <si>
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
@@ -902,7 +902,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1017,8 +1017,8 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
   </si>
   <si>
     <t>初期記録にはない報告</t>
@@ -1045,7 +1045,7 @@
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
 ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
-厚生労働省標準であるHOT9コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
+厚生労働省標準であるHOT9コード、HOT13コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
 なお、上記のいずれの標準的コードも付番されていない医薬品や医療材料の場合には、薬機法の下で使用されているGS1標準の識別コードであるGTIN(Global Trade Item Number)の調剤包装単位（最少包装単位、個別包装単位）14桁を使用する。  
 ひとつの処方薬、医療材料を複数のコード体系のコードで記述してもよく、その場合にcoding 要素を繰り返して記述する。  
 ただし、ひとつの処方薬を複数のコードで繰り返し記述する場合には、それらのコードが指し示す処方薬、医療材料は当然同一でなければならない。  
@@ -1140,7 +1140,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1166,7 +1166,7 @@
 </t>
   </si>
   <si>
-    <t>この処方オーダが最初に記述された日</t>
+    <t>この処方オーダが最初に記述された日時</t>
   </si>
   <si>
     <t>JP Coreでは必須。処方指示が最初に作成された日時。秒の精度まで記録する。タイムゾーンも付与しなければならない。</t>
@@ -1286,7 +1286,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1360,7 +1360,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1409,7 +1409,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -1814,7 +1814,7 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -1826,7 +1826,7 @@
     <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
@@ -2003,7 +2003,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2026,7 +2026,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2045,7 +2045,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -2368,17 +2368,17 @@
   <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2387,27 +2387,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="178.55859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.55078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="59.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
